--- a/docs/보고서/김도혁_프로젝트활동_정리.xlsx
+++ b/docs/보고서/김도혁_프로젝트활동_정리.xlsx
@@ -12,15 +12,13 @@
     <sheet sheetId="6" name="제외된 항목" state="visible" r:id="rId9"/>
     <sheet sheetId="7" name="확인 필요 항목" state="visible" r:id="rId10"/>
     <sheet sheetId="8" name="회의록 요약" state="visible" r:id="rId11"/>
-    <sheet sheetId="9" name="피드백" state="visible" r:id="rId12"/>
-    <sheet sheetId="10" name="WBS 업무 목록" state="visible" r:id="rId13"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2138" uniqueCount="1279">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2193" uniqueCount="1315">
   <si>
     <t>프로젝트</t>
   </si>
@@ -37,7 +35,7 @@
     <t>조사 범위</t>
   </si>
   <si>
-    <t>Git 커밋 전체 이력(전 브랜치) + Notion 회의록 19건 + 피드백 4건 + WBS 데이터베이스</t>
+    <t>Git 커밋 전체 이력(전 브랜치) + Notion 회의록 19건</t>
   </si>
   <si>
     <t>총 커밋 수</t>
@@ -64,7 +62,7 @@
     <t>주요 기여 영역</t>
   </si>
   <si>
-    <t>채팅 시스템(1:1→플로팅 위젯), 프로필 페이지 전면 구현, 방렌트/구인구직/중고거래 URL 필터 아키텍처, 관리자(Admin) 운영 패널, 인증/로그인 보안(Redis), KTS·KPPS 신뢰도 점수 시스템, AI 챗봇(멀티 LLM), Kanto GO 지도 보조기능, SEO/성능 최적화, 공통 UI 시스템화, 접근성 개선</t>
+    <t>채팅 시스템(1:1→플로팅 위젯), 프로필 페이지 전면 구현, 방렌트/구인구직/중고거래 URL 필터 아키텍처, 관리자(Admin) 운영 패널(super_admin 권한 체계), 인증/로그인 보안(Redis), KTS·KPPS 신뢰도 점수 시스템, AI 챗봇(멀티 LLM), Kanto GO 지도 보조기능, SEO/성능 최적화, 공통 UI 시스템화, 접근성 개선</t>
   </si>
   <si>
     <t>참고</t>
@@ -3556,7 +3554,7 @@
     <t>05/31</t>
   </si>
   <si>
-    <t>팀 성향 체크: "좁고 깊은것이 좋아요" 라고 답변. 1차/2차 배포 로드맵 팀 전체 논의.</t>
+    <t>팀 성향 체크: "깊게 생각해보고 체계화 시키는것을 좋아해요"라고 답변. 1차/2차 배포 로드맵 팀 전체 논의.</t>
   </si>
   <si>
     <t>06/01</t>
@@ -3857,6 +3855,114 @@
   </si>
   <si>
     <t>2026-06-23~06-30</t>
+  </si>
+  <si>
+    <t>369개 (전체 브랜치, 이메일 기준)</t>
+  </si>
+  <si>
+    <t>2026-05-29 ~ 2026-07-07 (약 5.7주)</t>
+  </si>
+  <si>
+    <t>2026-07-07</t>
+  </si>
+  <si>
+    <t>2026-07-06 11:55</t>
+  </si>
+  <si>
+    <t>166e6edd2f</t>
+  </si>
+  <si>
+    <t>chore: 문서 추가 및 리드미 수정</t>
+  </si>
+  <si>
+    <t>2026-07-06 18:13</t>
+  </si>
+  <si>
+    <t>3e81e07617</t>
+  </si>
+  <si>
+    <t>docs: Supabase pg_cron 스케줄 통합 정리</t>
+  </si>
+  <si>
+    <t>2026-07-06 18:18</t>
+  </si>
+  <si>
+    <t>08a55eb06d</t>
+  </si>
+  <si>
+    <t>chore: 미사용 DB 테이블 정리 및 스키마 문서 추가</t>
+  </si>
+  <si>
+    <t>2026-07-06 18:31</t>
+  </si>
+  <si>
+    <t>257ae18767</t>
+  </si>
+  <si>
+    <t>fix: 삭제된 테이블 참조 함수 및 중복 트리거 정리</t>
+  </si>
+  <si>
+    <t>2026-07-06 18:35</t>
+  </si>
+  <si>
+    <t>252b23ad12</t>
+  </si>
+  <si>
+    <t>docs: 성능 개선 배포 후 재측정 결과 반영 및 회귀 원인 조사</t>
+  </si>
+  <si>
+    <t>2026-07-06 23:41</t>
+  </si>
+  <si>
+    <t>acb02561ed</t>
+  </si>
+  <si>
+    <t>feat(signup): 약관을 선로딩하고 가입 완료 후 메인으로 이동</t>
+  </si>
+  <si>
+    <t>2026-07-07 10:11</t>
+  </si>
+  <si>
+    <t>cd05f926fb</t>
+  </si>
+  <si>
+    <t>docs: 보고서 추가</t>
+  </si>
+  <si>
+    <t>2026-07-07 10:16</t>
+  </si>
+  <si>
+    <t>c561da4f9f</t>
+  </si>
+  <si>
+    <t>docs: ESLint 오류 수정</t>
+  </si>
+  <si>
+    <t>2026-07-07 10:24</t>
+  </si>
+  <si>
+    <t>edf41749bd</t>
+  </si>
+  <si>
+    <t>docs: yml 파일 추가 (리포트 배포 페이지)</t>
+  </si>
+  <si>
+    <t>2026-07-07 10:26</t>
+  </si>
+  <si>
+    <t>a32785fac9</t>
+  </si>
+  <si>
+    <t>chore: 노드 24기반으로 변경</t>
+  </si>
+  <si>
+    <t>2026-07-07 12:06</t>
+  </si>
+  <si>
+    <t>7a87ebc263</t>
+  </si>
+  <si>
+    <t>chore: 보고서 수정</t>
   </si>
 </sst>
 </file>
@@ -4296,7 +4402,7 @@
         <v>6</v>
       </c>
       <c r="B4" t="s">
-        <v>7</v>
+        <v>1279</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -4304,7 +4410,7 @@
         <v>8</v>
       </c>
       <c r="B5" t="s">
-        <v>9</v>
+        <v>1280</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
@@ -4312,7 +4418,7 @@
         <v>10</v>
       </c>
       <c r="B6" t="s">
-        <v>11</v>
+        <v>1281</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
@@ -4337,448 +4443,6 @@
       </c>
       <c r="B9" t="s">
         <v>16</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E25"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
-  <cols>
-    <col min="1" max="1" width="40" customWidth="1"/>
-    <col min="2" max="3" width="12" customWidth="1"/>
-    <col min="4" max="4" width="20" customWidth="1"/>
-    <col min="5" max="5" width="16" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>1219</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1220</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>1221</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>1222</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>1223</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>1224</v>
-      </c>
-      <c r="B2" t="s">
-        <v>1225</v>
-      </c>
-      <c r="C2" t="s">
-        <v>1226</v>
-      </c>
-      <c r="D2" t="s">
-        <v>1227</v>
-      </c>
-      <c r="E2" t="s">
-        <v>1228</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>1229</v>
-      </c>
-      <c r="B3" t="s">
-        <v>1230</v>
-      </c>
-      <c r="C3" t="s">
-        <v>1226</v>
-      </c>
-      <c r="D3" t="s">
-        <v>1231</v>
-      </c>
-      <c r="E3" t="s">
-        <v>1228</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>1232</v>
-      </c>
-      <c r="B4" t="s">
-        <v>1230</v>
-      </c>
-      <c r="C4" t="s">
-        <v>1226</v>
-      </c>
-      <c r="D4" t="s">
-        <v>1233</v>
-      </c>
-      <c r="E4" t="s">
-        <v>1228</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>1234</v>
-      </c>
-      <c r="B5" t="s">
-        <v>1230</v>
-      </c>
-      <c r="C5" t="s">
-        <v>1226</v>
-      </c>
-      <c r="D5" t="s">
-        <v>1235</v>
-      </c>
-      <c r="E5" t="s">
-        <v>1236</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>1237</v>
-      </c>
-      <c r="B6" t="s">
-        <v>1230</v>
-      </c>
-      <c r="C6" t="s">
-        <v>1226</v>
-      </c>
-      <c r="D6" t="s">
-        <v>1235</v>
-      </c>
-      <c r="E6" t="s">
-        <v>1228</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>1238</v>
-      </c>
-      <c r="B7" t="s">
-        <v>1230</v>
-      </c>
-      <c r="C7" t="s">
-        <v>1226</v>
-      </c>
-      <c r="D7" t="s">
-        <v>1235</v>
-      </c>
-      <c r="E7" t="s">
-        <v>1236</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>1239</v>
-      </c>
-      <c r="B8" t="s">
-        <v>1230</v>
-      </c>
-      <c r="C8" t="s">
-        <v>1226</v>
-      </c>
-      <c r="D8" t="s">
-        <v>1240</v>
-      </c>
-      <c r="E8" t="s">
-        <v>1228</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>1241</v>
-      </c>
-      <c r="B9" t="s">
-        <v>1242</v>
-      </c>
-      <c r="C9" t="s">
-        <v>1226</v>
-      </c>
-      <c r="D9" t="s">
-        <v>1243</v>
-      </c>
-      <c r="E9" t="s">
-        <v>1228</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>1244</v>
-      </c>
-      <c r="B10" t="s">
-        <v>1242</v>
-      </c>
-      <c r="C10" t="s">
-        <v>1226</v>
-      </c>
-      <c r="D10" t="s">
-        <v>1245</v>
-      </c>
-      <c r="E10" t="s">
-        <v>1246</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>1247</v>
-      </c>
-      <c r="B11" t="s">
-        <v>1242</v>
-      </c>
-      <c r="C11" t="s">
-        <v>1226</v>
-      </c>
-      <c r="D11" t="s">
-        <v>1248</v>
-      </c>
-      <c r="E11" t="s">
-        <v>1246</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>1249</v>
-      </c>
-      <c r="B12" t="s">
-        <v>1242</v>
-      </c>
-      <c r="C12" t="s">
-        <v>1226</v>
-      </c>
-      <c r="D12" t="s">
-        <v>1250</v>
-      </c>
-      <c r="E12" t="s">
-        <v>1246</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>1251</v>
-      </c>
-      <c r="B13" t="s">
-        <v>1242</v>
-      </c>
-      <c r="C13" t="s">
-        <v>1226</v>
-      </c>
-      <c r="D13" t="s">
-        <v>1250</v>
-      </c>
-      <c r="E13" t="s">
-        <v>1246</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>1252</v>
-      </c>
-      <c r="B14" t="s">
-        <v>1253</v>
-      </c>
-      <c r="C14" t="s">
-        <v>1226</v>
-      </c>
-      <c r="D14" t="s">
-        <v>1254</v>
-      </c>
-      <c r="E14" t="s">
-        <v>1246</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>1255</v>
-      </c>
-      <c r="B15" t="s">
-        <v>1253</v>
-      </c>
-      <c r="C15" t="s">
-        <v>1226</v>
-      </c>
-      <c r="D15" t="s">
-        <v>1256</v>
-      </c>
-      <c r="E15" t="s">
-        <v>1236</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>1257</v>
-      </c>
-      <c r="B16" t="s">
-        <v>1242</v>
-      </c>
-      <c r="C16" t="s">
-        <v>1226</v>
-      </c>
-      <c r="D16" t="s">
-        <v>1258</v>
-      </c>
-      <c r="E16" t="s">
-        <v>1228</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>1259</v>
-      </c>
-      <c r="B17" t="s">
-        <v>1260</v>
-      </c>
-      <c r="C17" t="s">
-        <v>1226</v>
-      </c>
-      <c r="D17" t="s">
-        <v>1261</v>
-      </c>
-      <c r="E17" t="s">
-        <v>1236</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>571</v>
-      </c>
-      <c r="B18" t="s">
-        <v>1242</v>
-      </c>
-      <c r="C18" t="s">
-        <v>1226</v>
-      </c>
-      <c r="D18" t="s">
-        <v>1262</v>
-      </c>
-      <c r="E18" t="s">
-        <v>1228</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>1263</v>
-      </c>
-      <c r="B19" t="s">
-        <v>1260</v>
-      </c>
-      <c r="C19" t="s">
-        <v>1226</v>
-      </c>
-      <c r="D19" t="s">
-        <v>1264</v>
-      </c>
-      <c r="E19" t="s">
-        <v>1228</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>1265</v>
-      </c>
-      <c r="B20" t="s">
-        <v>1260</v>
-      </c>
-      <c r="C20" t="s">
-        <v>1226</v>
-      </c>
-      <c r="D20" t="s">
-        <v>1266</v>
-      </c>
-      <c r="E20" t="s">
-        <v>1228</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>1267</v>
-      </c>
-      <c r="B21" t="s">
-        <v>1230</v>
-      </c>
-      <c r="C21" t="s">
-        <v>1226</v>
-      </c>
-      <c r="D21" t="s">
-        <v>1268</v>
-      </c>
-      <c r="E21" t="s">
-        <v>1246</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>1269</v>
-      </c>
-      <c r="B22" t="s">
-        <v>1230</v>
-      </c>
-      <c r="C22" t="s">
-        <v>1226</v>
-      </c>
-      <c r="D22" t="s">
-        <v>1268</v>
-      </c>
-      <c r="E22" t="s">
-        <v>1246</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>1270</v>
-      </c>
-      <c r="B23" t="s">
-        <v>1271</v>
-      </c>
-      <c r="C23" t="s">
-        <v>1226</v>
-      </c>
-      <c r="D23" t="s">
-        <v>1272</v>
-      </c>
-      <c r="E23" t="s">
-        <v>1273</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>1274</v>
-      </c>
-      <c r="B24" t="s">
-        <v>1230</v>
-      </c>
-      <c r="C24" t="s">
-        <v>1226</v>
-      </c>
-      <c r="D24" t="s">
-        <v>1275</v>
-      </c>
-      <c r="E24" t="s">
-        <v>1228</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>1276</v>
-      </c>
-      <c r="B25" t="s">
-        <v>1230</v>
-      </c>
-      <c r="C25" t="s">
-        <v>1277</v>
-      </c>
-      <c r="D25" t="s">
-        <v>1278</v>
-      </c>
-      <c r="E25" t="s">
-        <v>1246</v>
       </c>
     </row>
   </sheetData>
@@ -4789,7 +4453,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F359"/>
+  <dimension ref="A1:F370"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
@@ -11978,6 +11642,226 @@
       </c>
       <c r="F359" t="s">
         <v>1062</v>
+      </c>
+    </row>
+    <row r="360" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A360">
+        <v>359</v>
+      </c>
+      <c r="B360" t="s">
+        <v>1282</v>
+      </c>
+      <c r="C360" t="s">
+        <v>1283</v>
+      </c>
+      <c r="D360" t="s">
+        <v>33</v>
+      </c>
+      <c r="E360" t="s">
+        <v>77</v>
+      </c>
+      <c r="F360" t="s">
+        <v>1284</v>
+      </c>
+    </row>
+    <row r="361" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A361">
+        <v>360</v>
+      </c>
+      <c r="B361" t="s">
+        <v>1285</v>
+      </c>
+      <c r="C361" t="s">
+        <v>1286</v>
+      </c>
+      <c r="D361" t="s">
+        <v>112</v>
+      </c>
+      <c r="E361" t="s">
+        <v>323</v>
+      </c>
+      <c r="F361" t="s">
+        <v>1287</v>
+      </c>
+    </row>
+    <row r="362" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A362">
+        <v>361</v>
+      </c>
+      <c r="B362" t="s">
+        <v>1288</v>
+      </c>
+      <c r="C362" t="s">
+        <v>1289</v>
+      </c>
+      <c r="D362" t="s">
+        <v>33</v>
+      </c>
+      <c r="E362" t="s">
+        <v>323</v>
+      </c>
+      <c r="F362" t="s">
+        <v>1290</v>
+      </c>
+    </row>
+    <row r="363" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A363">
+        <v>362</v>
+      </c>
+      <c r="B363" t="s">
+        <v>1291</v>
+      </c>
+      <c r="C363" t="s">
+        <v>1292</v>
+      </c>
+      <c r="D363" t="s">
+        <v>73</v>
+      </c>
+      <c r="E363" t="s">
+        <v>323</v>
+      </c>
+      <c r="F363" t="s">
+        <v>1293</v>
+      </c>
+    </row>
+    <row r="364" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A364">
+        <v>363</v>
+      </c>
+      <c r="B364" t="s">
+        <v>1294</v>
+      </c>
+      <c r="C364" t="s">
+        <v>1295</v>
+      </c>
+      <c r="D364" t="s">
+        <v>112</v>
+      </c>
+      <c r="E364" t="s">
+        <v>340</v>
+      </c>
+      <c r="F364" t="s">
+        <v>1296</v>
+      </c>
+    </row>
+    <row r="365" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A365">
+        <v>364</v>
+      </c>
+      <c r="B365" t="s">
+        <v>1297</v>
+      </c>
+      <c r="C365" t="s">
+        <v>1298</v>
+      </c>
+      <c r="D365" t="s">
+        <v>25</v>
+      </c>
+      <c r="E365" t="s">
+        <v>408</v>
+      </c>
+      <c r="F365" t="s">
+        <v>1299</v>
+      </c>
+    </row>
+    <row r="366" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A366">
+        <v>365</v>
+      </c>
+      <c r="B366" t="s">
+        <v>1300</v>
+      </c>
+      <c r="C366" t="s">
+        <v>1301</v>
+      </c>
+      <c r="D366" t="s">
+        <v>112</v>
+      </c>
+      <c r="E366" t="s">
+        <v>77</v>
+      </c>
+      <c r="F366" t="s">
+        <v>1302</v>
+      </c>
+    </row>
+    <row r="367" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A367">
+        <v>366</v>
+      </c>
+      <c r="B367" t="s">
+        <v>1303</v>
+      </c>
+      <c r="C367" t="s">
+        <v>1304</v>
+      </c>
+      <c r="D367" t="s">
+        <v>112</v>
+      </c>
+      <c r="E367" t="s">
+        <v>323</v>
+      </c>
+      <c r="F367" t="s">
+        <v>1305</v>
+      </c>
+    </row>
+    <row r="368" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A368">
+        <v>367</v>
+      </c>
+      <c r="B368" t="s">
+        <v>1306</v>
+      </c>
+      <c r="C368" t="s">
+        <v>1307</v>
+      </c>
+      <c r="D368" t="s">
+        <v>112</v>
+      </c>
+      <c r="E368" t="s">
+        <v>323</v>
+      </c>
+      <c r="F368" t="s">
+        <v>1308</v>
+      </c>
+    </row>
+    <row r="369" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A369">
+        <v>368</v>
+      </c>
+      <c r="B369" t="s">
+        <v>1309</v>
+      </c>
+      <c r="C369" t="s">
+        <v>1310</v>
+      </c>
+      <c r="D369" t="s">
+        <v>33</v>
+      </c>
+      <c r="E369" t="s">
+        <v>323</v>
+      </c>
+      <c r="F369" t="s">
+        <v>1311</v>
+      </c>
+    </row>
+    <row r="370" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A370">
+        <v>369</v>
+      </c>
+      <c r="B370" t="s">
+        <v>1312</v>
+      </c>
+      <c r="C370" t="s">
+        <v>1313</v>
+      </c>
+      <c r="D370" t="s">
+        <v>33</v>
+      </c>
+      <c r="E370" t="s">
+        <v>77</v>
+      </c>
+      <c r="F370" t="s">
+        <v>1314</v>
       </c>
     </row>
   </sheetData>
@@ -12062,23 +11946,23 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>49</v>
+        <v>77</v>
       </c>
       <c r="B9">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>77</v>
+        <v>408</v>
       </c>
       <c r="B10">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>408</v>
+        <v>49</v>
       </c>
       <c r="B11">
         <v>15</v>
@@ -12086,15 +11970,15 @@
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>59</v>
+        <v>323</v>
       </c>
       <c r="B12">
-        <v>9</v>
+        <v>12</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>121</v>
+        <v>59</v>
       </c>
       <c r="B13">
         <v>9</v>
@@ -12102,7 +11986,7 @@
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>170</v>
+        <v>121</v>
       </c>
       <c r="B14">
         <v>9</v>
@@ -12110,7 +11994,7 @@
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>689</v>
+        <v>170</v>
       </c>
       <c r="B15">
         <v>9</v>
@@ -12118,10 +12002,10 @@
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>323</v>
+        <v>689</v>
       </c>
       <c r="B16">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
@@ -12145,7 +12029,7 @@
         <v>340</v>
       </c>
       <c r="B19">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
@@ -12192,7 +12076,7 @@
         <v>25</v>
       </c>
       <c r="B2">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -12200,7 +12084,7 @@
         <v>73</v>
       </c>
       <c r="B3">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -12208,7 +12092,7 @@
         <v>33</v>
       </c>
       <c r="B4">
-        <v>31</v>
+        <v>35</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -12240,7 +12124,7 @@
         <v>112</v>
       </c>
       <c r="B8">
-        <v>9</v>
+        <v>14</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
@@ -12908,59 +12792,4 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
-  <cols>
-    <col min="1" max="1" width="16" customWidth="1"/>
-    <col min="2" max="2" width="100" style="5" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>1173</v>
-      </c>
-      <c r="B1" s="6" t="s">
-        <v>1067</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>1211</v>
-      </c>
-      <c r="B2" s="5" t="s">
-        <v>1212</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>1213</v>
-      </c>
-      <c r="B3" s="5" t="s">
-        <v>1214</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>1215</v>
-      </c>
-      <c r="B4" s="5" t="s">
-        <v>1216</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>1217</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>1218</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
-</worksheet>
 </file>
--- a/docs/보고서/김도혁_프로젝트활동_정리.xlsx
+++ b/docs/보고서/김도혁_프로젝트활동_정리.xlsx
@@ -12,13 +12,15 @@
     <sheet sheetId="6" name="제외된 항목" state="visible" r:id="rId9"/>
     <sheet sheetId="7" name="확인 필요 항목" state="visible" r:id="rId10"/>
     <sheet sheetId="8" name="회의록 요약" state="visible" r:id="rId11"/>
+    <sheet sheetId="9" name="피드백" state="visible" r:id="rId12"/>
+    <sheet sheetId="10" name="WBS 업무 목록" state="visible" r:id="rId13"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2193" uniqueCount="1315">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2176" uniqueCount="1303">
   <si>
     <t>프로젝트</t>
   </si>
@@ -35,25 +37,25 @@
     <t>조사 범위</t>
   </si>
   <si>
-    <t>Git 커밋 전체 이력(전 브랜치) + Notion 회의록 19건</t>
+    <t>Git 커밋 전체 이력(전 브랜치) + Notion 회의록 19건 + 피드백 4건 + WBS 데이터베이스</t>
   </si>
   <si>
     <t>총 커밋 수</t>
   </si>
   <si>
-    <t>358개 (전체 브랜치, 이메일 기준)</t>
+    <t>365개 (main 브랜치, 동일 patch-id 중복 병합 제외)</t>
   </si>
   <si>
     <t>활동 기간</t>
   </si>
   <si>
-    <t>2026-05-29 ~ 2026-07-06 (약 5.5주)</t>
+    <t>2026-05-29 ~ 2026-07-06 (약 5.6주)</t>
   </si>
   <si>
     <t>보고서 생성일</t>
   </si>
   <si>
-    <t>2026-07-06</t>
+    <t>2026-07-07 (최초 작성 2026-07-06 이후 07-06 추가 커밋 7건 반영 재검토)</t>
   </si>
   <si>
     <t/>
@@ -62,7 +64,7 @@
     <t>주요 기여 영역</t>
   </si>
   <si>
-    <t>채팅 시스템(1:1→플로팅 위젯), 프로필 페이지 전면 구현, 방렌트/구인구직/중고거래 URL 필터 아키텍처, 관리자(Admin) 운영 패널(super_admin 권한 체계), 인증/로그인 보안(Redis), KTS·KPPS 신뢰도 점수 시스템, AI 챗봇(멀티 LLM), Kanto GO 지도 보조기능, SEO/성능 최적화, 공통 UI 시스템화, 접근성 개선</t>
+    <t>채팅 시스템(1:1→플로팅 위젯), 프로필 페이지 전면 구현, 방렌트/구인구직/중고거래 URL 필터 아키텍처, 관리자(Admin) 운영 패널, 인증/로그인 보안(Redis), KTS·KPPS 신뢰도 점수 시스템, AI 챗봇(멀티 LLM), Kanto GO 지도 보조기능, SEO/성능 최적화, 공통 UI 시스템화, 접근성 개선, DB 스키마 정리, 회원가입 약관 선로딩</t>
   </si>
   <si>
     <t>참고</t>
@@ -3209,6 +3211,69 @@
     <t>fix: GlobalLayout에서 Header에 initialNotices prop 누락 수정</t>
   </si>
   <si>
+    <t>2026-07-06 11:55</t>
+  </si>
+  <si>
+    <t>166e6edd2f</t>
+  </si>
+  <si>
+    <t>chore: 문서 추가 및 리드미 수정</t>
+  </si>
+  <si>
+    <t>2026-07-06 13:11</t>
+  </si>
+  <si>
+    <t>8c64b396a1</t>
+  </si>
+  <si>
+    <t>Remove contribution assessment section from README</t>
+  </si>
+  <si>
+    <t>2026-07-06 18:13</t>
+  </si>
+  <si>
+    <t>3e81e07617</t>
+  </si>
+  <si>
+    <t>docs: Supabase pg_cron 스케줄 통합 정리</t>
+  </si>
+  <si>
+    <t>2026-07-06 18:18</t>
+  </si>
+  <si>
+    <t>87a037d267</t>
+  </si>
+  <si>
+    <t>chore: 미사용 DB 테이블 정리 및 스키마 문서 추가</t>
+  </si>
+  <si>
+    <t>2026-07-06 18:31</t>
+  </si>
+  <si>
+    <t>257ae18767</t>
+  </si>
+  <si>
+    <t>fix: 삭제된 테이블 참조 함수 및 중복 트리거 정리</t>
+  </si>
+  <si>
+    <t>2026-07-06 18:35</t>
+  </si>
+  <si>
+    <t>9a4be1f58e</t>
+  </si>
+  <si>
+    <t>docs: 성능 개선 배포 후 재측정 결과 반영 및 회귀 원인 조사</t>
+  </si>
+  <si>
+    <t>2026-07-06 23:41</t>
+  </si>
+  <si>
+    <t>acb02561ed</t>
+  </si>
+  <si>
+    <t>feat(signup): 약관을 선로딩하고 가입 완료 후 메인으로 이동</t>
+  </si>
+  <si>
     <t>커밋 수</t>
   </si>
   <si>
@@ -3404,6 +3469,15 @@
     <t>핫픽스 브랜치 룰</t>
   </si>
   <si>
+    <t>#602</t>
+  </si>
+  <si>
+    <t>hotfix/v.1.3.1</t>
+  </si>
+  <si>
+    <t>DB 정리(미사용 테이블 삭제·참조 함수 수정), 성능 재측정+회귀 원인 규명, 회원가입 약관 선로딩(useSignupTerms)</t>
+  </si>
+  <si>
     <t>이 외 "Merge pull request" 커밋 작성자(병합 수행자)로 70건 등장 — 다른 팀원(THLIMM/soyu/dongkeun) 브랜치를 병합 담당한 경우 다수 포함되어 있어, 병합자=작성자로 확대 해석하지 않았음.</t>
   </si>
   <si>
@@ -3554,7 +3628,7 @@
     <t>05/31</t>
   </si>
   <si>
-    <t>팀 성향 체크: "깊게 생각해보고 체계화 시키는것을 좋아해요"라고 답변. 1차/2차 배포 로드맵 팀 전체 논의.</t>
+    <t>팀 성향 체크: "좁고 깊은것이 좋아요" 라고 답변. 1차/2차 배포 로드맵 팀 전체 논의.</t>
   </si>
   <si>
     <t>06/01</t>
@@ -3855,114 +3929,6 @@
   </si>
   <si>
     <t>2026-06-23~06-30</t>
-  </si>
-  <si>
-    <t>369개 (전체 브랜치, 이메일 기준)</t>
-  </si>
-  <si>
-    <t>2026-05-29 ~ 2026-07-07 (약 5.7주)</t>
-  </si>
-  <si>
-    <t>2026-07-07</t>
-  </si>
-  <si>
-    <t>2026-07-06 11:55</t>
-  </si>
-  <si>
-    <t>166e6edd2f</t>
-  </si>
-  <si>
-    <t>chore: 문서 추가 및 리드미 수정</t>
-  </si>
-  <si>
-    <t>2026-07-06 18:13</t>
-  </si>
-  <si>
-    <t>3e81e07617</t>
-  </si>
-  <si>
-    <t>docs: Supabase pg_cron 스케줄 통합 정리</t>
-  </si>
-  <si>
-    <t>2026-07-06 18:18</t>
-  </si>
-  <si>
-    <t>08a55eb06d</t>
-  </si>
-  <si>
-    <t>chore: 미사용 DB 테이블 정리 및 스키마 문서 추가</t>
-  </si>
-  <si>
-    <t>2026-07-06 18:31</t>
-  </si>
-  <si>
-    <t>257ae18767</t>
-  </si>
-  <si>
-    <t>fix: 삭제된 테이블 참조 함수 및 중복 트리거 정리</t>
-  </si>
-  <si>
-    <t>2026-07-06 18:35</t>
-  </si>
-  <si>
-    <t>252b23ad12</t>
-  </si>
-  <si>
-    <t>docs: 성능 개선 배포 후 재측정 결과 반영 및 회귀 원인 조사</t>
-  </si>
-  <si>
-    <t>2026-07-06 23:41</t>
-  </si>
-  <si>
-    <t>acb02561ed</t>
-  </si>
-  <si>
-    <t>feat(signup): 약관을 선로딩하고 가입 완료 후 메인으로 이동</t>
-  </si>
-  <si>
-    <t>2026-07-07 10:11</t>
-  </si>
-  <si>
-    <t>cd05f926fb</t>
-  </si>
-  <si>
-    <t>docs: 보고서 추가</t>
-  </si>
-  <si>
-    <t>2026-07-07 10:16</t>
-  </si>
-  <si>
-    <t>c561da4f9f</t>
-  </si>
-  <si>
-    <t>docs: ESLint 오류 수정</t>
-  </si>
-  <si>
-    <t>2026-07-07 10:24</t>
-  </si>
-  <si>
-    <t>edf41749bd</t>
-  </si>
-  <si>
-    <t>docs: yml 파일 추가 (리포트 배포 페이지)</t>
-  </si>
-  <si>
-    <t>2026-07-07 10:26</t>
-  </si>
-  <si>
-    <t>a32785fac9</t>
-  </si>
-  <si>
-    <t>chore: 노드 24기반으로 변경</t>
-  </si>
-  <si>
-    <t>2026-07-07 12:06</t>
-  </si>
-  <si>
-    <t>7a87ebc263</t>
-  </si>
-  <si>
-    <t>chore: 보고서 수정</t>
   </si>
 </sst>
 </file>
@@ -4402,7 +4368,7 @@
         <v>6</v>
       </c>
       <c r="B4" t="s">
-        <v>1279</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -4410,7 +4376,7 @@
         <v>8</v>
       </c>
       <c r="B5" t="s">
-        <v>1280</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
@@ -4418,7 +4384,7 @@
         <v>10</v>
       </c>
       <c r="B6" t="s">
-        <v>1281</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
@@ -4443,6 +4409,448 @@
       </c>
       <c r="B9" t="s">
         <v>16</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:E25"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="40" customWidth="1"/>
+    <col min="2" max="3" width="12" customWidth="1"/>
+    <col min="4" max="4" width="20" customWidth="1"/>
+    <col min="5" max="5" width="16" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>1243</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1244</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>1245</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>1246</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>1247</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>1248</v>
+      </c>
+      <c r="B2" t="s">
+        <v>1249</v>
+      </c>
+      <c r="C2" t="s">
+        <v>1250</v>
+      </c>
+      <c r="D2" t="s">
+        <v>1251</v>
+      </c>
+      <c r="E2" t="s">
+        <v>1252</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>1253</v>
+      </c>
+      <c r="B3" t="s">
+        <v>1254</v>
+      </c>
+      <c r="C3" t="s">
+        <v>1250</v>
+      </c>
+      <c r="D3" t="s">
+        <v>1255</v>
+      </c>
+      <c r="E3" t="s">
+        <v>1252</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>1256</v>
+      </c>
+      <c r="B4" t="s">
+        <v>1254</v>
+      </c>
+      <c r="C4" t="s">
+        <v>1250</v>
+      </c>
+      <c r="D4" t="s">
+        <v>1257</v>
+      </c>
+      <c r="E4" t="s">
+        <v>1252</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>1258</v>
+      </c>
+      <c r="B5" t="s">
+        <v>1254</v>
+      </c>
+      <c r="C5" t="s">
+        <v>1250</v>
+      </c>
+      <c r="D5" t="s">
+        <v>1259</v>
+      </c>
+      <c r="E5" t="s">
+        <v>1260</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>1261</v>
+      </c>
+      <c r="B6" t="s">
+        <v>1254</v>
+      </c>
+      <c r="C6" t="s">
+        <v>1250</v>
+      </c>
+      <c r="D6" t="s">
+        <v>1259</v>
+      </c>
+      <c r="E6" t="s">
+        <v>1252</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>1262</v>
+      </c>
+      <c r="B7" t="s">
+        <v>1254</v>
+      </c>
+      <c r="C7" t="s">
+        <v>1250</v>
+      </c>
+      <c r="D7" t="s">
+        <v>1259</v>
+      </c>
+      <c r="E7" t="s">
+        <v>1260</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>1263</v>
+      </c>
+      <c r="B8" t="s">
+        <v>1254</v>
+      </c>
+      <c r="C8" t="s">
+        <v>1250</v>
+      </c>
+      <c r="D8" t="s">
+        <v>1264</v>
+      </c>
+      <c r="E8" t="s">
+        <v>1252</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>1265</v>
+      </c>
+      <c r="B9" t="s">
+        <v>1266</v>
+      </c>
+      <c r="C9" t="s">
+        <v>1250</v>
+      </c>
+      <c r="D9" t="s">
+        <v>1267</v>
+      </c>
+      <c r="E9" t="s">
+        <v>1252</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>1268</v>
+      </c>
+      <c r="B10" t="s">
+        <v>1266</v>
+      </c>
+      <c r="C10" t="s">
+        <v>1250</v>
+      </c>
+      <c r="D10" t="s">
+        <v>1269</v>
+      </c>
+      <c r="E10" t="s">
+        <v>1270</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>1271</v>
+      </c>
+      <c r="B11" t="s">
+        <v>1266</v>
+      </c>
+      <c r="C11" t="s">
+        <v>1250</v>
+      </c>
+      <c r="D11" t="s">
+        <v>1272</v>
+      </c>
+      <c r="E11" t="s">
+        <v>1270</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>1273</v>
+      </c>
+      <c r="B12" t="s">
+        <v>1266</v>
+      </c>
+      <c r="C12" t="s">
+        <v>1250</v>
+      </c>
+      <c r="D12" t="s">
+        <v>1274</v>
+      </c>
+      <c r="E12" t="s">
+        <v>1270</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>1275</v>
+      </c>
+      <c r="B13" t="s">
+        <v>1266</v>
+      </c>
+      <c r="C13" t="s">
+        <v>1250</v>
+      </c>
+      <c r="D13" t="s">
+        <v>1274</v>
+      </c>
+      <c r="E13" t="s">
+        <v>1270</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>1276</v>
+      </c>
+      <c r="B14" t="s">
+        <v>1277</v>
+      </c>
+      <c r="C14" t="s">
+        <v>1250</v>
+      </c>
+      <c r="D14" t="s">
+        <v>1278</v>
+      </c>
+      <c r="E14" t="s">
+        <v>1270</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>1279</v>
+      </c>
+      <c r="B15" t="s">
+        <v>1277</v>
+      </c>
+      <c r="C15" t="s">
+        <v>1250</v>
+      </c>
+      <c r="D15" t="s">
+        <v>1280</v>
+      </c>
+      <c r="E15" t="s">
+        <v>1260</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>1281</v>
+      </c>
+      <c r="B16" t="s">
+        <v>1266</v>
+      </c>
+      <c r="C16" t="s">
+        <v>1250</v>
+      </c>
+      <c r="D16" t="s">
+        <v>1282</v>
+      </c>
+      <c r="E16" t="s">
+        <v>1252</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>1283</v>
+      </c>
+      <c r="B17" t="s">
+        <v>1284</v>
+      </c>
+      <c r="C17" t="s">
+        <v>1250</v>
+      </c>
+      <c r="D17" t="s">
+        <v>1285</v>
+      </c>
+      <c r="E17" t="s">
+        <v>1260</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>571</v>
+      </c>
+      <c r="B18" t="s">
+        <v>1266</v>
+      </c>
+      <c r="C18" t="s">
+        <v>1250</v>
+      </c>
+      <c r="D18" t="s">
+        <v>1286</v>
+      </c>
+      <c r="E18" t="s">
+        <v>1252</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>1287</v>
+      </c>
+      <c r="B19" t="s">
+        <v>1284</v>
+      </c>
+      <c r="C19" t="s">
+        <v>1250</v>
+      </c>
+      <c r="D19" t="s">
+        <v>1288</v>
+      </c>
+      <c r="E19" t="s">
+        <v>1252</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>1289</v>
+      </c>
+      <c r="B20" t="s">
+        <v>1284</v>
+      </c>
+      <c r="C20" t="s">
+        <v>1250</v>
+      </c>
+      <c r="D20" t="s">
+        <v>1290</v>
+      </c>
+      <c r="E20" t="s">
+        <v>1252</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>1291</v>
+      </c>
+      <c r="B21" t="s">
+        <v>1254</v>
+      </c>
+      <c r="C21" t="s">
+        <v>1250</v>
+      </c>
+      <c r="D21" t="s">
+        <v>1292</v>
+      </c>
+      <c r="E21" t="s">
+        <v>1270</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>1293</v>
+      </c>
+      <c r="B22" t="s">
+        <v>1254</v>
+      </c>
+      <c r="C22" t="s">
+        <v>1250</v>
+      </c>
+      <c r="D22" t="s">
+        <v>1292</v>
+      </c>
+      <c r="E22" t="s">
+        <v>1270</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>1294</v>
+      </c>
+      <c r="B23" t="s">
+        <v>1295</v>
+      </c>
+      <c r="C23" t="s">
+        <v>1250</v>
+      </c>
+      <c r="D23" t="s">
+        <v>1296</v>
+      </c>
+      <c r="E23" t="s">
+        <v>1297</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>1298</v>
+      </c>
+      <c r="B24" t="s">
+        <v>1254</v>
+      </c>
+      <c r="C24" t="s">
+        <v>1250</v>
+      </c>
+      <c r="D24" t="s">
+        <v>1299</v>
+      </c>
+      <c r="E24" t="s">
+        <v>1252</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>1300</v>
+      </c>
+      <c r="B25" t="s">
+        <v>1254</v>
+      </c>
+      <c r="C25" t="s">
+        <v>1301</v>
+      </c>
+      <c r="D25" t="s">
+        <v>1302</v>
+      </c>
+      <c r="E25" t="s">
+        <v>1270</v>
       </c>
     </row>
   </sheetData>
@@ -4453,7 +4861,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F370"/>
+  <dimension ref="A1:F366"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
@@ -11649,10 +12057,10 @@
         <v>359</v>
       </c>
       <c r="B360" t="s">
-        <v>1282</v>
+        <v>1063</v>
       </c>
       <c r="C360" t="s">
-        <v>1283</v>
+        <v>1064</v>
       </c>
       <c r="D360" t="s">
         <v>33</v>
@@ -11661,7 +12069,7 @@
         <v>77</v>
       </c>
       <c r="F360" t="s">
-        <v>1284</v>
+        <v>1065</v>
       </c>
     </row>
     <row r="361" spans="1:6" x14ac:dyDescent="0.25">
@@ -11669,19 +12077,19 @@
         <v>360</v>
       </c>
       <c r="B361" t="s">
-        <v>1285</v>
+        <v>1066</v>
       </c>
       <c r="C361" t="s">
-        <v>1286</v>
+        <v>1067</v>
       </c>
       <c r="D361" t="s">
-        <v>112</v>
+        <v>732</v>
       </c>
       <c r="E361" t="s">
-        <v>323</v>
+        <v>26</v>
       </c>
       <c r="F361" t="s">
-        <v>1287</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="362" spans="1:6" x14ac:dyDescent="0.25">
@@ -11689,19 +12097,19 @@
         <v>361</v>
       </c>
       <c r="B362" t="s">
-        <v>1288</v>
+        <v>1069</v>
       </c>
       <c r="C362" t="s">
-        <v>1289</v>
+        <v>1070</v>
       </c>
       <c r="D362" t="s">
-        <v>33</v>
+        <v>112</v>
       </c>
       <c r="E362" t="s">
-        <v>323</v>
+        <v>77</v>
       </c>
       <c r="F362" t="s">
-        <v>1290</v>
+        <v>1071</v>
       </c>
     </row>
     <row r="363" spans="1:6" x14ac:dyDescent="0.25">
@@ -11709,19 +12117,19 @@
         <v>362</v>
       </c>
       <c r="B363" t="s">
-        <v>1291</v>
+        <v>1072</v>
       </c>
       <c r="C363" t="s">
-        <v>1292</v>
+        <v>1073</v>
       </c>
       <c r="D363" t="s">
-        <v>73</v>
+        <v>33</v>
       </c>
       <c r="E363" t="s">
-        <v>323</v>
+        <v>77</v>
       </c>
       <c r="F363" t="s">
-        <v>1293</v>
+        <v>1074</v>
       </c>
     </row>
     <row r="364" spans="1:6" x14ac:dyDescent="0.25">
@@ -11729,19 +12137,19 @@
         <v>363</v>
       </c>
       <c r="B364" t="s">
-        <v>1294</v>
+        <v>1075</v>
       </c>
       <c r="C364" t="s">
-        <v>1295</v>
+        <v>1076</v>
       </c>
       <c r="D364" t="s">
-        <v>112</v>
+        <v>73</v>
       </c>
       <c r="E364" t="s">
-        <v>340</v>
+        <v>26</v>
       </c>
       <c r="F364" t="s">
-        <v>1296</v>
+        <v>1077</v>
       </c>
     </row>
     <row r="365" spans="1:6" x14ac:dyDescent="0.25">
@@ -11749,19 +12157,19 @@
         <v>364</v>
       </c>
       <c r="B365" t="s">
-        <v>1297</v>
+        <v>1078</v>
       </c>
       <c r="C365" t="s">
-        <v>1298</v>
+        <v>1079</v>
       </c>
       <c r="D365" t="s">
-        <v>25</v>
+        <v>112</v>
       </c>
       <c r="E365" t="s">
-        <v>408</v>
+        <v>340</v>
       </c>
       <c r="F365" t="s">
-        <v>1299</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="366" spans="1:6" x14ac:dyDescent="0.25">
@@ -11769,99 +12177,19 @@
         <v>365</v>
       </c>
       <c r="B366" t="s">
-        <v>1300</v>
+        <v>1081</v>
       </c>
       <c r="C366" t="s">
-        <v>1301</v>
+        <v>1082</v>
       </c>
       <c r="D366" t="s">
-        <v>112</v>
+        <v>25</v>
       </c>
       <c r="E366" t="s">
-        <v>77</v>
+        <v>170</v>
       </c>
       <c r="F366" t="s">
-        <v>1302</v>
-      </c>
-    </row>
-    <row r="367" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A367">
-        <v>366</v>
-      </c>
-      <c r="B367" t="s">
-        <v>1303</v>
-      </c>
-      <c r="C367" t="s">
-        <v>1304</v>
-      </c>
-      <c r="D367" t="s">
-        <v>112</v>
-      </c>
-      <c r="E367" t="s">
-        <v>323</v>
-      </c>
-      <c r="F367" t="s">
-        <v>1305</v>
-      </c>
-    </row>
-    <row r="368" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A368">
-        <v>367</v>
-      </c>
-      <c r="B368" t="s">
-        <v>1306</v>
-      </c>
-      <c r="C368" t="s">
-        <v>1307</v>
-      </c>
-      <c r="D368" t="s">
-        <v>112</v>
-      </c>
-      <c r="E368" t="s">
-        <v>323</v>
-      </c>
-      <c r="F368" t="s">
-        <v>1308</v>
-      </c>
-    </row>
-    <row r="369" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A369">
-        <v>368</v>
-      </c>
-      <c r="B369" t="s">
-        <v>1309</v>
-      </c>
-      <c r="C369" t="s">
-        <v>1310</v>
-      </c>
-      <c r="D369" t="s">
-        <v>33</v>
-      </c>
-      <c r="E369" t="s">
-        <v>323</v>
-      </c>
-      <c r="F369" t="s">
-        <v>1311</v>
-      </c>
-    </row>
-    <row r="370" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A370">
-        <v>369</v>
-      </c>
-      <c r="B370" t="s">
-        <v>1312</v>
-      </c>
-      <c r="C370" t="s">
-        <v>1313</v>
-      </c>
-      <c r="D370" t="s">
-        <v>33</v>
-      </c>
-      <c r="E370" t="s">
-        <v>77</v>
-      </c>
-      <c r="F370" t="s">
-        <v>1314</v>
+        <v>1083</v>
       </c>
     </row>
   </sheetData>
@@ -11885,7 +12213,7 @@
         <v>21</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1063</v>
+        <v>1084</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
@@ -11893,7 +12221,7 @@
         <v>26</v>
       </c>
       <c r="B2">
-        <v>124</v>
+        <v>126</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -11938,7 +12266,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>483</v>
+        <v>77</v>
       </c>
       <c r="B8">
         <v>18</v>
@@ -11946,7 +12274,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>77</v>
+        <v>483</v>
       </c>
       <c r="B9">
         <v>18</v>
@@ -11954,15 +12282,15 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>408</v>
+        <v>49</v>
       </c>
       <c r="B10">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>49</v>
+        <v>408</v>
       </c>
       <c r="B11">
         <v>15</v>
@@ -11970,10 +12298,10 @@
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>323</v>
+        <v>170</v>
       </c>
       <c r="B12">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
@@ -11994,7 +12322,7 @@
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>170</v>
+        <v>689</v>
       </c>
       <c r="B15">
         <v>9</v>
@@ -12002,10 +12330,10 @@
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>689</v>
+        <v>323</v>
       </c>
       <c r="B16">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
@@ -12018,7 +12346,7 @@
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>666</v>
+        <v>340</v>
       </c>
       <c r="B18">
         <v>5</v>
@@ -12026,7 +12354,7 @@
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>340</v>
+        <v>666</v>
       </c>
       <c r="B19">
         <v>5</v>
@@ -12065,10 +12393,10 @@
   <sheetData>
     <row r="1" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>1064</v>
+        <v>1085</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1063</v>
+        <v>1084</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
@@ -12092,7 +12420,7 @@
         <v>33</v>
       </c>
       <c r="B4">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -12124,7 +12452,7 @@
         <v>112</v>
       </c>
       <c r="B8">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
@@ -12148,7 +12476,7 @@
         <v>732</v>
       </c>
       <c r="B11">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -12159,7 +12487,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C24"/>
+  <dimension ref="A1:C25"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -12169,43 +12497,43 @@
   <sheetData>
     <row r="1" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>1065</v>
+        <v>1086</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1066</v>
+        <v>1087</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>1067</v>
+        <v>1088</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>1068</v>
+        <v>1089</v>
       </c>
       <c r="B2" t="s">
-        <v>1069</v>
+        <v>1090</v>
       </c>
       <c r="C2" t="s">
-        <v>1070</v>
+        <v>1091</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>1071</v>
+        <v>1092</v>
       </c>
       <c r="B3" t="s">
-        <v>1072</v>
+        <v>1093</v>
       </c>
       <c r="C3" t="s">
-        <v>1073</v>
+        <v>1094</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>1074</v>
+        <v>1095</v>
       </c>
       <c r="B4" t="s">
-        <v>1075</v>
+        <v>1096</v>
       </c>
       <c r="C4" t="s">
         <v>59</v>
@@ -12213,131 +12541,131 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>1076</v>
+        <v>1097</v>
       </c>
       <c r="B5" t="s">
-        <v>1077</v>
+        <v>1098</v>
       </c>
       <c r="C5" t="s">
-        <v>1078</v>
+        <v>1099</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>1079</v>
+        <v>1100</v>
       </c>
       <c r="B6" t="s">
-        <v>1080</v>
+        <v>1101</v>
       </c>
       <c r="C6" t="s">
-        <v>1081</v>
+        <v>1102</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>1082</v>
+        <v>1103</v>
       </c>
       <c r="B7" t="s">
-        <v>1083</v>
+        <v>1104</v>
       </c>
       <c r="C7" t="s">
-        <v>1084</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>1085</v>
+        <v>1106</v>
       </c>
       <c r="B8" t="s">
-        <v>1086</v>
+        <v>1107</v>
       </c>
       <c r="C8" t="s">
-        <v>1087</v>
+        <v>1108</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>1088</v>
+        <v>1109</v>
       </c>
       <c r="B9" t="s">
-        <v>1086</v>
+        <v>1107</v>
       </c>
       <c r="C9" t="s">
-        <v>1089</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>1090</v>
+        <v>1111</v>
       </c>
       <c r="B10" t="s">
-        <v>1091</v>
+        <v>1112</v>
       </c>
       <c r="C10" t="s">
-        <v>1092</v>
+        <v>1113</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>1093</v>
+        <v>1114</v>
       </c>
       <c r="B11" t="s">
-        <v>1094</v>
+        <v>1115</v>
       </c>
       <c r="C11" t="s">
-        <v>1095</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>1096</v>
+        <v>1117</v>
       </c>
       <c r="B12" t="s">
-        <v>1097</v>
+        <v>1118</v>
       </c>
       <c r="C12" t="s">
-        <v>1098</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>1099</v>
+        <v>1120</v>
       </c>
       <c r="B13" t="s">
-        <v>1100</v>
+        <v>1121</v>
       </c>
       <c r="C13" t="s">
-        <v>1101</v>
+        <v>1122</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>1102</v>
+        <v>1123</v>
       </c>
       <c r="B14" t="s">
-        <v>1103</v>
+        <v>1124</v>
       </c>
       <c r="C14" t="s">
-        <v>1104</v>
+        <v>1125</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>1105</v>
+        <v>1126</v>
       </c>
       <c r="B15" t="s">
-        <v>1106</v>
+        <v>1127</v>
       </c>
       <c r="C15" t="s">
-        <v>1107</v>
+        <v>1128</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>1108</v>
+        <v>1129</v>
       </c>
       <c r="B16" t="s">
-        <v>1109</v>
+        <v>1130</v>
       </c>
       <c r="C16" t="s">
         <v>689</v>
@@ -12345,79 +12673,90 @@
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>1110</v>
+        <v>1131</v>
       </c>
       <c r="B17" t="s">
-        <v>1111</v>
+        <v>1132</v>
       </c>
       <c r="C17" t="s">
-        <v>1112</v>
+        <v>1133</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>1113</v>
+        <v>1134</v>
       </c>
       <c r="B18" t="s">
-        <v>1114</v>
+        <v>1135</v>
       </c>
       <c r="C18" t="s">
-        <v>1115</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>1116</v>
+        <v>1137</v>
       </c>
       <c r="B19" t="s">
-        <v>1117</v>
+        <v>1138</v>
       </c>
       <c r="C19" t="s">
-        <v>1118</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>1119</v>
+        <v>1140</v>
       </c>
       <c r="B20" t="s">
-        <v>1120</v>
+        <v>1141</v>
       </c>
       <c r="C20" t="s">
-        <v>1121</v>
+        <v>1142</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>1122</v>
+        <v>1143</v>
       </c>
       <c r="B21" t="s">
-        <v>1123</v>
+        <v>1144</v>
       </c>
       <c r="C21" t="s">
-        <v>1124</v>
+        <v>1145</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>1125</v>
+        <v>1146</v>
       </c>
       <c r="B22" t="s">
-        <v>1126</v>
+        <v>1147</v>
       </c>
       <c r="C22" t="s">
-        <v>1127</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
+        <v>1148</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>1149</v>
+      </c>
+      <c r="B23" t="s">
+        <v>1150</v>
+      </c>
+      <c r="C23" t="s">
+        <v>1151</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
         <v>15</v>
       </c>
-      <c r="B24" t="s">
+      <c r="B25" t="s">
         <v>12</v>
       </c>
-      <c r="C24" t="s">
-        <v>1128</v>
+      <c r="C25" t="s">
+        <v>1152</v>
       </c>
     </row>
   </sheetData>
@@ -12440,104 +12779,104 @@
   <sheetData>
     <row r="1" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>1129</v>
+        <v>1153</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>1130</v>
+        <v>1154</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>1131</v>
+        <v>1155</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>1132</v>
+        <v>1156</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>1133</v>
+        <v>1157</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>1134</v>
+        <v>1158</v>
       </c>
       <c r="B2" t="s">
-        <v>1135</v>
+        <v>1159</v>
       </c>
       <c r="C2" t="s">
-        <v>1136</v>
+        <v>1160</v>
       </c>
       <c r="D2" t="s">
-        <v>1137</v>
+        <v>1161</v>
       </c>
       <c r="E2" t="s">
-        <v>1138</v>
+        <v>1162</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>1139</v>
+        <v>1163</v>
       </c>
       <c r="B3" t="s">
         <v>723</v>
       </c>
       <c r="C3" t="s">
-        <v>1140</v>
+        <v>1164</v>
       </c>
       <c r="D3" t="s">
-        <v>1141</v>
+        <v>1165</v>
       </c>
       <c r="E3" t="s">
-        <v>1142</v>
+        <v>1166</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>1143</v>
+        <v>1167</v>
       </c>
       <c r="B4" t="s">
-        <v>1144</v>
+        <v>1168</v>
       </c>
       <c r="C4" t="s">
-        <v>1145</v>
+        <v>1169</v>
       </c>
       <c r="D4" t="s">
-        <v>1146</v>
+        <v>1170</v>
       </c>
       <c r="E4" t="s">
-        <v>1147</v>
+        <v>1171</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>1148</v>
+        <v>1172</v>
       </c>
       <c r="B5" t="s">
-        <v>1149</v>
+        <v>1173</v>
       </c>
       <c r="C5" t="s">
-        <v>1150</v>
+        <v>1174</v>
       </c>
       <c r="D5" t="s">
-        <v>1151</v>
+        <v>1175</v>
       </c>
       <c r="E5" t="s">
-        <v>1152</v>
+        <v>1176</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>1153</v>
+        <v>1177</v>
       </c>
       <c r="B6" t="s">
-        <v>1154</v>
+        <v>1178</v>
       </c>
       <c r="C6" t="s">
-        <v>1155</v>
+        <v>1179</v>
       </c>
       <c r="D6" t="s">
-        <v>1156</v>
+        <v>1180</v>
       </c>
       <c r="E6" t="s">
-        <v>1157</v>
+        <v>1181</v>
       </c>
     </row>
   </sheetData>
@@ -12557,68 +12896,68 @@
   <sheetData>
     <row r="1" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>1129</v>
+        <v>1153</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1067</v>
+        <v>1088</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>1158</v>
+        <v>1182</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>1159</v>
+        <v>1183</v>
       </c>
       <c r="B2" t="s">
-        <v>1160</v>
+        <v>1184</v>
       </c>
       <c r="C2" t="s">
-        <v>1161</v>
+        <v>1185</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>1162</v>
+        <v>1186</v>
       </c>
       <c r="B3" t="s">
-        <v>1163</v>
+        <v>1187</v>
       </c>
       <c r="C3" t="s">
-        <v>1164</v>
+        <v>1188</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>1165</v>
+        <v>1189</v>
       </c>
       <c r="B4" t="s">
-        <v>1166</v>
+        <v>1190</v>
       </c>
       <c r="C4" t="s">
-        <v>1167</v>
+        <v>1191</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>1168</v>
+        <v>1192</v>
       </c>
       <c r="B5" t="s">
-        <v>1166</v>
+        <v>1190</v>
       </c>
       <c r="C5" t="s">
-        <v>1169</v>
+        <v>1193</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>1170</v>
+        <v>1194</v>
       </c>
       <c r="B6" t="s">
-        <v>1171</v>
+        <v>1195</v>
       </c>
       <c r="C6" t="s">
-        <v>1172</v>
+        <v>1196</v>
       </c>
     </row>
   </sheetData>
@@ -12638,154 +12977,209 @@
   <sheetData>
     <row r="1" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>1173</v>
+        <v>1197</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>1174</v>
+        <v>1198</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>1175</v>
+        <v>1199</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>1176</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>1177</v>
+        <v>1201</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>1178</v>
+        <v>1202</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>1179</v>
+        <v>1203</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>1180</v>
+        <v>1204</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>1181</v>
+        <v>1205</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>1182</v>
+        <v>1206</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>1183</v>
+        <v>1207</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>1184</v>
+        <v>1208</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>1185</v>
+        <v>1209</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>1186</v>
+        <v>1210</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>1187</v>
+        <v>1211</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>1188</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>1189</v>
+        <v>1213</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>1190</v>
+        <v>1214</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>1191</v>
+        <v>1215</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>1192</v>
+        <v>1216</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>1193</v>
+        <v>1217</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>1194</v>
+        <v>1218</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>1195</v>
+        <v>1219</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>1196</v>
+        <v>1220</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>1197</v>
+        <v>1221</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>1198</v>
+        <v>1222</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>1199</v>
+        <v>1223</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>1200</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>1201</v>
+        <v>1225</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>1202</v>
+        <v>1226</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>1203</v>
+        <v>1227</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>1204</v>
+        <v>1228</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>1205</v>
+        <v>1229</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>1206</v>
+        <v>1230</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>1207</v>
+        <v>1231</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>1208</v>
+        <v>1232</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>1209</v>
+        <v>1233</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>1210</v>
+        <v>1234</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:B5"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="16" customWidth="1"/>
+    <col min="2" max="2" width="100" style="5" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>1197</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>1088</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>1235</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>1236</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>1237</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>1239</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>1240</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>1241</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>1242</v>
       </c>
     </row>
   </sheetData>
